--- a/registration_forms/018_equine_facilitator_training_registration--registration_forms.xlsx
+++ b/registration_forms/018_equine_facilitator_training_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'6-1',_'name':_'less_than_1_year',_'label':_'less_than_1_year'}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '6-1', 'name': 'Less than 1 year', 'label': 'Less than 1 year'}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'6-2',_'name':_'1-2_years',_'label':_'1-2_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '6-2', 'name': '1-2 years', 'label': '1-2 years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'6-3',_'name':_'2-5_years',_'label':_'2-5_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '6-3', 'name': '2-5 years', 'label': '2-5 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'6-4',_'name':_'more_than_5_years',_'label':_'more_than_5_years'}</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '6-4', 'name': 'More than 5 years', 'label': 'More than 5 years'}</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'7-1',_'name':_'no_experience',_'label':_'no_experience'}</t>
+          <t>no_experience</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '7-1', 'name': 'No experience', 'label': 'No experience'}</t>
+          <t>No experience</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'7-2',_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '7-2', 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'7-3',_'name':_'prefer_not_to_say',_'label':_'prefer_not_to_say'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '7-3', 'name': 'Prefer not to say', 'label': 'Prefer not to say'}</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'8-1',_'name':_'certified',_'label':_'certified'}</t>
+          <t>certified</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '8-1', 'name': 'Certified', 'label': 'Certified'}</t>
+          <t>Certified</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'8-2',_'name':_'not_certified',_'label':_'not_certified'}</t>
+          <t>not_certified</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '8-2', 'name': 'Not Certified', 'label': 'Not Certified'}</t>
+          <t>Not Certified</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'10-1',_'name':_'10:00-11:30',_'label':_'10:00-11:30'}</t>
+          <t>10:00-11:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '10-1', 'name': '10:00-11:30', 'label': '10:00-11:30'}</t>
+          <t>10:00-11:30</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'10-2',_'name':_'13:00-14:00',_'label':_'13:00-14:00'}</t>
+          <t>13:00-14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '10-2', 'name': '13:00-14:00', 'label': '13:00-14:00'}</t>
+          <t>13:00-14:00</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'10-3',_'name':_'16:00-17:00',_'label':_'16:00-17:00'}</t>
+          <t>16:00-17:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '10-3', 'name': '16:00-17:00', 'label': '16:00-17:00'}</t>
+          <t>16:00-17:00</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'11-1',_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': '11-1', 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'11-2',_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': '11-2', 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
